--- a/artfynd/A 38016-2025 artfynd.xlsx
+++ b/artfynd/A 38016-2025 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128466256</v>
+        <v>128466229</v>
       </c>
       <c r="B2" t="n">
-        <v>98476</v>
+        <v>56864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462557</v>
+        <v>462535</v>
       </c>
       <c r="R2" t="n">
-        <v>6696922</v>
+        <v>6696898</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>20-tal bladrosetter.</t>
+          <t>Balningsgrop.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,53 +795,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128466229</v>
+        <v>128466256</v>
       </c>
       <c r="B3" t="n">
-        <v>56864</v>
+        <v>98478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462535</v>
+        <v>462557</v>
       </c>
       <c r="R3" t="n">
-        <v>6696898</v>
+        <v>6696922</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,12 +875,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Balningsgrop.</t>
+          <t>20-tal bladrosetter.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,45 +907,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128466222</v>
+        <v>128466224</v>
       </c>
       <c r="B4" t="n">
-        <v>91323</v>
+        <v>57673</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462417</v>
+        <v>462469</v>
       </c>
       <c r="R4" t="n">
-        <v>6697315</v>
+        <v>6697194</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +995,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,53 +1027,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128466224</v>
+        <v>128466222</v>
       </c>
       <c r="B5" t="n">
-        <v>57673</v>
+        <v>91325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>462469</v>
+        <v>462417</v>
       </c>
       <c r="R5" t="n">
-        <v>6697194</v>
+        <v>6697315</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1097,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1102,12 +1107,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,43 +1134,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128466221</v>
+        <v>128466265</v>
       </c>
       <c r="B6" t="n">
-        <v>5197</v>
+        <v>79032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1178,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462534</v>
+        <v>462675</v>
       </c>
       <c r="R6" t="n">
-        <v>6697251</v>
+        <v>6696895</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1217,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På tallstam.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128466265</v>
+        <v>128466260</v>
       </c>
       <c r="B7" t="n">
         <v>79032</v>
@@ -1289,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>462675</v>
+        <v>462377</v>
       </c>
       <c r="R7" t="n">
-        <v>6696895</v>
+        <v>6697267</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1483,37 +1482,43 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128466260</v>
+        <v>128466221</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>5197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1521,10 +1526,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462377</v>
+        <v>462534</v>
       </c>
       <c r="R9" t="n">
-        <v>6697267</v>
+        <v>6697251</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,12 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På tallstam.</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,32 +1599,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128466254</v>
+        <v>128466231</v>
       </c>
       <c r="B10" t="n">
-        <v>98476</v>
+        <v>57833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462554</v>
+        <v>462657</v>
       </c>
       <c r="R10" t="n">
-        <v>6696921</v>
+        <v>6696882</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,12 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>20-tal bladrosetter.</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1830,32 +1825,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128466253</v>
+        <v>128466254</v>
       </c>
       <c r="B12" t="n">
-        <v>78790</v>
+        <v>98478</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1865,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>462421</v>
+        <v>462554</v>
       </c>
       <c r="R12" t="n">
-        <v>6697341</v>
+        <v>6696921</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1905,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>20-tal bladrosetter.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128466231</v>
+        <v>128466253</v>
       </c>
       <c r="B13" t="n">
-        <v>57833</v>
+        <v>78790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1948,21 +1948,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>462657</v>
+        <v>462421</v>
       </c>
       <c r="R13" t="n">
-        <v>6696882</v>
+        <v>6697341</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,7 +2047,7 @@
         <v>128466234</v>
       </c>
       <c r="B14" t="n">
-        <v>91378</v>
+        <v>91380</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>128466270</v>
       </c>
       <c r="B16" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,10 +2381,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128466243</v>
+        <v>128466249</v>
       </c>
       <c r="B17" t="n">
-        <v>78791</v>
+        <v>78790</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2392,21 +2392,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>462628</v>
+        <v>462756</v>
       </c>
       <c r="R17" t="n">
-        <v>6696967</v>
+        <v>6696647</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2488,10 +2488,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128466249</v>
+        <v>128466244</v>
       </c>
       <c r="B18" t="n">
-        <v>78790</v>
+        <v>78791</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2499,21 +2499,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>462756</v>
+        <v>462583</v>
       </c>
       <c r="R18" t="n">
-        <v>6696647</v>
+        <v>6696944</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2595,7 +2595,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128466244</v>
+        <v>128466243</v>
       </c>
       <c r="B19" t="n">
         <v>78791</v>
@@ -2630,10 +2630,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>462583</v>
+        <v>462628</v>
       </c>
       <c r="R19" t="n">
-        <v>6696944</v>
+        <v>6696967</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2705,7 +2705,7 @@
         <v>128466271</v>
       </c>
       <c r="B20" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128466232</v>
+        <v>128466227</v>
       </c>
       <c r="B21" t="n">
-        <v>57833</v>
+        <v>57673</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2820,33 +2820,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2856,10 +2852,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>462418</v>
+        <v>462484</v>
       </c>
       <c r="R21" t="n">
-        <v>6697314</v>
+        <v>6697200</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2891,7 +2887,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2901,7 +2897,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2928,10 +2929,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128466227</v>
+        <v>128466232</v>
       </c>
       <c r="B22" t="n">
-        <v>57673</v>
+        <v>57833</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2939,29 +2940,33 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2971,10 +2976,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>462484</v>
+        <v>462418</v>
       </c>
       <c r="R22" t="n">
-        <v>6697200</v>
+        <v>6697314</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3006,7 +3011,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3016,12 +3021,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3048,53 +3048,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128466225</v>
+        <v>128466272</v>
       </c>
       <c r="B23" t="n">
-        <v>57673</v>
+        <v>92650</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>462768</v>
+        <v>462727</v>
       </c>
       <c r="R23" t="n">
-        <v>6696701</v>
+        <v>6696783</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3126,7 +3118,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3136,12 +3128,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:47</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3168,45 +3155,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128466272</v>
+        <v>128466225</v>
       </c>
       <c r="B24" t="n">
-        <v>92648</v>
+        <v>57673</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>462727</v>
+        <v>462768</v>
       </c>
       <c r="R24" t="n">
-        <v>6696783</v>
+        <v>6696701</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3238,7 +3233,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3248,7 +3243,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3385,7 +3385,7 @@
         <v>128466235</v>
       </c>
       <c r="B26" t="n">
-        <v>91378</v>
+        <v>91380</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3493,10 +3493,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128466269</v>
+        <v>128466238</v>
       </c>
       <c r="B27" t="n">
-        <v>79032</v>
+        <v>91380</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3504,34 +3504,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>462378</v>
+        <v>462777</v>
       </c>
       <c r="R27" t="n">
-        <v>6697317</v>
+        <v>6696623</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3563,7 +3566,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3573,7 +3576,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3582,6 +3585,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3600,10 +3604,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128466238</v>
+        <v>128466269</v>
       </c>
       <c r="B28" t="n">
-        <v>91378</v>
+        <v>79032</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3611,37 +3615,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>462777</v>
+        <v>462378</v>
       </c>
       <c r="R28" t="n">
-        <v>6696623</v>
+        <v>6697317</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3673,7 +3674,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3683,7 +3684,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3692,7 +3693,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4063,10 +4063,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128466226</v>
+        <v>128466264</v>
       </c>
       <c r="B32" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4074,31 +4074,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4106,10 +4101,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>462534</v>
+        <v>462644</v>
       </c>
       <c r="R32" t="n">
-        <v>6696943</v>
+        <v>6696869</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4141,7 +4136,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4151,12 +4146,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska ringhack på äldre gran, rikligt nästan hela trädet.</t>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4165,6 +4160,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4299,10 +4295,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128466264</v>
+        <v>128466226</v>
       </c>
       <c r="B34" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4310,26 +4306,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4337,10 +4338,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>462644</v>
+        <v>462534</v>
       </c>
       <c r="R34" t="n">
-        <v>6696869</v>
+        <v>6696943</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4372,7 +4373,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4382,12 +4383,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På tallstam</t>
+          <t>Färska ringhack på äldre gran, rikligt nästan hela trädet.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4396,7 +4397,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4415,45 +4415,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128466273</v>
+        <v>128466233</v>
       </c>
       <c r="B35" t="n">
-        <v>92648</v>
+        <v>91380</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>462356</v>
+        <v>462380</v>
       </c>
       <c r="R35" t="n">
-        <v>6697346</v>
+        <v>6697276</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4485,7 +4488,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4495,7 +4498,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4504,6 +4507,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4522,48 +4526,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128466233</v>
+        <v>128466273</v>
       </c>
       <c r="B36" t="n">
-        <v>91378</v>
+        <v>92650</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>462380</v>
+        <v>462356</v>
       </c>
       <c r="R36" t="n">
-        <v>6697276</v>
+        <v>6697346</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4595,7 +4596,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4605,7 +4606,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4614,7 +4615,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4740,32 +4740,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128466275</v>
+        <v>128466261</v>
       </c>
       <c r="B38" t="n">
-        <v>92648</v>
+        <v>79032</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>462670</v>
+        <v>462748</v>
       </c>
       <c r="R38" t="n">
-        <v>6696759</v>
+        <v>6696705</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4823,7 +4823,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På tallstam.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4851,32 +4856,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128466261</v>
+        <v>128466275</v>
       </c>
       <c r="B39" t="n">
-        <v>79032</v>
+        <v>92650</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4889,10 +4894,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>462748</v>
+        <v>462670</v>
       </c>
       <c r="R39" t="n">
-        <v>6696705</v>
+        <v>6696759</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4924,7 +4929,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4934,12 +4939,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På tallstam.</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5083,32 +5083,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128466257</v>
+        <v>128466250</v>
       </c>
       <c r="B41" t="n">
-        <v>98476</v>
+        <v>78790</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>462535</v>
+        <v>462525</v>
       </c>
       <c r="R41" t="n">
-        <v>6696918</v>
+        <v>6696905</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5163,12 +5163,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>20-tal bladrosetter.</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5195,57 +5190,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128466277</v>
+        <v>128466257</v>
       </c>
       <c r="B42" t="n">
-        <v>96601</v>
+        <v>98478</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>462757</v>
+        <v>462535</v>
       </c>
       <c r="R42" t="n">
-        <v>6696682</v>
+        <v>6696918</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5277,7 +5260,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5287,12 +5270,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ca.</t>
+          <t>20-tal bladrosetter.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5301,7 +5284,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5320,37 +5302,46 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128466236</v>
+        <v>128466277</v>
       </c>
       <c r="B43" t="n">
-        <v>91378</v>
+        <v>96603</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5442</v>
+        <v>2869</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5358,10 +5349,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>462733</v>
+        <v>462757</v>
       </c>
       <c r="R43" t="n">
-        <v>6696654</v>
+        <v>6696682</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5393,7 +5384,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5403,7 +5394,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ca.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5431,10 +5427,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128466250</v>
+        <v>128466236</v>
       </c>
       <c r="B44" t="n">
-        <v>78790</v>
+        <v>91380</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5442,34 +5438,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Länsmansberget Väster, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>462525</v>
+        <v>462733</v>
       </c>
       <c r="R44" t="n">
-        <v>6696905</v>
+        <v>6696654</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5501,7 +5500,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5511,7 +5510,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5520,6 +5519,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38016-2025 artfynd.xlsx
+++ b/artfynd/A 38016-2025 artfynd.xlsx
@@ -3827,10 +3827,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128466262</v>
+        <v>128466223</v>
       </c>
       <c r="B30" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3838,26 +3838,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3865,10 +3870,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>462731</v>
+        <v>462561</v>
       </c>
       <c r="R30" t="n">
-        <v>6696782</v>
+        <v>6697006</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3900,7 +3905,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3910,12 +3915,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På äldre grövre tallstam.</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3924,7 +3929,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3943,10 +3947,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128466223</v>
+        <v>128466262</v>
       </c>
       <c r="B31" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3954,31 +3958,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3986,10 +3985,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>462561</v>
+        <v>462731</v>
       </c>
       <c r="R31" t="n">
-        <v>6697006</v>
+        <v>6696782</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4021,7 +4020,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4031,12 +4030,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>På äldre grövre tallstam.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4045,6 +4044,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38016-2025 artfynd.xlsx
+++ b/artfynd/A 38016-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128466229</v>
       </c>
       <c r="B2" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>128466256</v>
       </c>
       <c r="B3" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128466224</v>
       </c>
       <c r="B4" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>128466222</v>
       </c>
       <c r="B5" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>128466265</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>128466260</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>128466266</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>128466231</v>
       </c>
       <c r="B10" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>128466230</v>
       </c>
       <c r="B11" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>128466254</v>
       </c>
       <c r="B12" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>128466253</v>
       </c>
       <c r="B13" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>128466234</v>
       </c>
       <c r="B14" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>128466270</v>
       </c>
       <c r="B16" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>128466249</v>
       </c>
       <c r="B17" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>128466244</v>
       </c>
       <c r="B18" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>128466243</v>
       </c>
       <c r="B19" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>128466271</v>
       </c>
       <c r="B20" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128466227</v>
       </c>
       <c r="B21" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>128466232</v>
       </c>
       <c r="B22" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>128466272</v>
       </c>
       <c r="B23" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>128466225</v>
       </c>
       <c r="B24" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>128466235</v>
       </c>
       <c r="B26" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>128466238</v>
       </c>
       <c r="B27" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>128466269</v>
       </c>
       <c r="B28" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>128466263</v>
       </c>
       <c r="B29" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>128466223</v>
       </c>
       <c r="B30" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>128466262</v>
       </c>
       <c r="B31" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>128466264</v>
       </c>
       <c r="B32" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>128466258</v>
       </c>
       <c r="B33" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>128466226</v>
       </c>
       <c r="B34" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>128466233</v>
       </c>
       <c r="B35" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>128466273</v>
       </c>
       <c r="B36" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>128466268</v>
       </c>
       <c r="B37" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>128466261</v>
       </c>
       <c r="B38" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>128466275</v>
       </c>
       <c r="B39" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>128466267</v>
       </c>
       <c r="B40" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>128466250</v>
       </c>
       <c r="B41" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>128466257</v>
       </c>
       <c r="B42" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>128466277</v>
       </c>
       <c r="B43" t="n">
-        <v>96603</v>
+        <v>96696</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>128466236</v>
       </c>
       <c r="B44" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5536,6 +5536,130 @@
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128466239</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57682</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Länsmansberget Väster, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>462507</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6697019</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre stor tall med spillkråkehål.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38016-2025 artfynd.xlsx
+++ b/artfynd/A 38016-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128466229</v>
       </c>
       <c r="B2" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>128466256</v>
       </c>
       <c r="B3" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128466224</v>
       </c>
       <c r="B4" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>128466222</v>
       </c>
       <c r="B5" t="n">
-        <v>91417</v>
+        <v>91423</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>128466265</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>128466260</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>128466266</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>128466231</v>
       </c>
       <c r="B10" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>128466230</v>
       </c>
       <c r="B11" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>128466254</v>
       </c>
       <c r="B12" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>128466253</v>
       </c>
       <c r="B13" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>128466234</v>
       </c>
       <c r="B14" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>128466270</v>
       </c>
       <c r="B16" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>128466249</v>
       </c>
       <c r="B17" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>128466244</v>
       </c>
       <c r="B18" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>128466243</v>
       </c>
       <c r="B19" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>128466271</v>
       </c>
       <c r="B20" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128466227</v>
       </c>
       <c r="B21" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>128466232</v>
       </c>
       <c r="B22" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>128466272</v>
       </c>
       <c r="B23" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>128466225</v>
       </c>
       <c r="B24" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>128466235</v>
       </c>
       <c r="B26" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>128466238</v>
       </c>
       <c r="B27" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>128466269</v>
       </c>
       <c r="B28" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>128466263</v>
       </c>
       <c r="B29" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>128466223</v>
       </c>
       <c r="B30" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>128466262</v>
       </c>
       <c r="B31" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>128466264</v>
       </c>
       <c r="B32" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>128466258</v>
       </c>
       <c r="B33" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>128466226</v>
       </c>
       <c r="B34" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>128466233</v>
       </c>
       <c r="B35" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>128466273</v>
       </c>
       <c r="B36" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>128466268</v>
       </c>
       <c r="B37" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>128466261</v>
       </c>
       <c r="B38" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>128466275</v>
       </c>
       <c r="B39" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>128466267</v>
       </c>
       <c r="B40" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>128466250</v>
       </c>
       <c r="B41" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>128466257</v>
       </c>
       <c r="B42" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>128466277</v>
       </c>
       <c r="B43" t="n">
-        <v>96696</v>
+        <v>96702</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>128466236</v>
       </c>
       <c r="B44" t="n">
-        <v>91472</v>
+        <v>91478</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>128466239</v>
       </c>
       <c r="B45" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 38016-2025 artfynd.xlsx
+++ b/artfynd/A 38016-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>128466256</v>
       </c>
       <c r="B3" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>128466222</v>
       </c>
       <c r="B5" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>128466254</v>
       </c>
       <c r="B12" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>128466234</v>
       </c>
       <c r="B14" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>128466270</v>
       </c>
       <c r="B16" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>128466271</v>
       </c>
       <c r="B20" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>128466272</v>
       </c>
       <c r="B23" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>128466235</v>
       </c>
       <c r="B26" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>128466238</v>
       </c>
       <c r="B27" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>128466233</v>
       </c>
       <c r="B35" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>128466273</v>
       </c>
       <c r="B36" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>128466275</v>
       </c>
       <c r="B39" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>128466257</v>
       </c>
       <c r="B42" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>128466277</v>
       </c>
       <c r="B43" t="n">
-        <v>96702</v>
+        <v>96708</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>128466236</v>
       </c>
       <c r="B44" t="n">
-        <v>91478</v>
+        <v>91484</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 38016-2025 artfynd.xlsx
+++ b/artfynd/A 38016-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>128466256</v>
       </c>
       <c r="B3" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>128466222</v>
       </c>
       <c r="B5" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>128466265</v>
       </c>
       <c r="B6" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>128466260</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>128466266</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>128466254</v>
       </c>
       <c r="B12" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>128466253</v>
       </c>
       <c r="B13" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>128466234</v>
       </c>
       <c r="B14" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>128466270</v>
       </c>
       <c r="B16" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>128466249</v>
       </c>
       <c r="B17" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>128466244</v>
       </c>
       <c r="B18" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>128466243</v>
       </c>
       <c r="B19" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>128466271</v>
       </c>
       <c r="B20" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>128466272</v>
       </c>
       <c r="B23" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>128466235</v>
       </c>
       <c r="B26" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>128466238</v>
       </c>
       <c r="B27" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>128466269</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>128466263</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>128466262</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>128466264</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>128466258</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>128466233</v>
       </c>
       <c r="B35" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>128466273</v>
       </c>
       <c r="B36" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>128466268</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>128466261</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>128466275</v>
       </c>
       <c r="B39" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>128466267</v>
       </c>
       <c r="B40" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>128466250</v>
       </c>
       <c r="B41" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>128466257</v>
       </c>
       <c r="B42" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>128466277</v>
       </c>
       <c r="B43" t="n">
-        <v>96708</v>
+        <v>96710</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>128466236</v>
       </c>
       <c r="B44" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 38016-2025 artfynd.xlsx
+++ b/artfynd/A 38016-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>128466256</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>128466254</v>
       </c>
       <c r="B12" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>128466257</v>
       </c>
       <c r="B42" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 38016-2025 artfynd.xlsx
+++ b/artfynd/A 38016-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>128466256</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>128466222</v>
       </c>
       <c r="B5" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>128466254</v>
       </c>
       <c r="B12" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>128466234</v>
       </c>
       <c r="B14" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>128466270</v>
       </c>
       <c r="B16" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>128466271</v>
       </c>
       <c r="B20" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>128466272</v>
       </c>
       <c r="B23" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>128466235</v>
       </c>
       <c r="B26" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>128466238</v>
       </c>
       <c r="B27" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>128466233</v>
       </c>
       <c r="B35" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>128466273</v>
       </c>
       <c r="B36" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>128466275</v>
       </c>
       <c r="B39" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>128466257</v>
       </c>
       <c r="B42" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>128466277</v>
       </c>
       <c r="B43" t="n">
-        <v>96710</v>
+        <v>96711</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>128466236</v>
       </c>
       <c r="B44" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 38016-2025 artfynd.xlsx
+++ b/artfynd/A 38016-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128466229</v>
       </c>
       <c r="B2" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>128466256</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>128466224</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>128466222</v>
       </c>
       <c r="B5" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>128466265</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>128466260</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>128466266</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
         <v>128466231</v>
       </c>
       <c r="B10" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>128466230</v>
       </c>
       <c r="B11" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>128466254</v>
       </c>
       <c r="B12" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>128466253</v>
       </c>
       <c r="B13" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>128466234</v>
       </c>
       <c r="B14" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>128466270</v>
       </c>
       <c r="B16" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>128466249</v>
       </c>
       <c r="B17" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>128466244</v>
       </c>
       <c r="B18" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>128466243</v>
       </c>
       <c r="B19" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>128466271</v>
       </c>
       <c r="B20" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128466227</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>128466232</v>
       </c>
       <c r="B22" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>128466272</v>
       </c>
       <c r="B23" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>128466225</v>
       </c>
       <c r="B24" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>128466235</v>
       </c>
       <c r="B26" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>128466238</v>
       </c>
       <c r="B27" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>128466269</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>128466263</v>
       </c>
       <c r="B29" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>128466223</v>
       </c>
       <c r="B30" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>128466262</v>
       </c>
       <c r="B31" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>128466264</v>
       </c>
       <c r="B32" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>128466258</v>
       </c>
       <c r="B33" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>128466226</v>
       </c>
       <c r="B34" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>128466233</v>
       </c>
       <c r="B35" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>128466273</v>
       </c>
       <c r="B36" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>128466268</v>
       </c>
       <c r="B37" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>128466261</v>
       </c>
       <c r="B38" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>128466275</v>
       </c>
       <c r="B39" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>128466267</v>
       </c>
       <c r="B40" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>128466250</v>
       </c>
       <c r="B41" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>128466257</v>
       </c>
       <c r="B42" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>128466277</v>
       </c>
       <c r="B43" t="n">
-        <v>96711</v>
+        <v>96738</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>128466236</v>
       </c>
       <c r="B44" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>128466239</v>
       </c>
       <c r="B45" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 38016-2025 artfynd.xlsx
+++ b/artfynd/A 38016-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>128466256</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>128466222</v>
       </c>
       <c r="B5" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>128466265</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>128466260</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>128466266</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>128466254</v>
       </c>
       <c r="B12" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>128466253</v>
       </c>
       <c r="B13" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>128466234</v>
       </c>
       <c r="B14" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>128466270</v>
       </c>
       <c r="B16" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>128466249</v>
       </c>
       <c r="B17" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>128466244</v>
       </c>
       <c r="B18" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>128466243</v>
       </c>
       <c r="B19" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>128466271</v>
       </c>
       <c r="B20" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>128466272</v>
       </c>
       <c r="B23" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>128466235</v>
       </c>
       <c r="B26" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>128466238</v>
       </c>
       <c r="B27" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>128466269</v>
       </c>
       <c r="B28" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>128466263</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>128466262</v>
       </c>
       <c r="B31" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>128466264</v>
       </c>
       <c r="B32" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>128466258</v>
       </c>
       <c r="B33" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>128466233</v>
       </c>
       <c r="B35" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>128466273</v>
       </c>
       <c r="B36" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>128466268</v>
       </c>
       <c r="B37" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>128466261</v>
       </c>
       <c r="B38" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>128466275</v>
       </c>
       <c r="B39" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>128466267</v>
       </c>
       <c r="B40" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>128466250</v>
       </c>
       <c r="B41" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>128466257</v>
       </c>
       <c r="B42" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>128466277</v>
       </c>
       <c r="B43" t="n">
-        <v>96738</v>
+        <v>96744</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>128466236</v>
       </c>
       <c r="B44" t="n">
-        <v>91514</v>
+        <v>91519</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 38016-2025 artfynd.xlsx
+++ b/artfynd/A 38016-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>128466256</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         <v>128466222</v>
       </c>
       <c r="B5" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>128466254</v>
       </c>
       <c r="B12" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>128466234</v>
       </c>
       <c r="B14" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>128466270</v>
       </c>
       <c r="B16" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>128466271</v>
       </c>
       <c r="B20" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>128466272</v>
       </c>
       <c r="B23" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>128466235</v>
       </c>
       <c r="B26" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>128466238</v>
       </c>
       <c r="B27" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         <v>128466233</v>
       </c>
       <c r="B35" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>128466273</v>
       </c>
       <c r="B36" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>128466275</v>
       </c>
       <c r="B39" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>128466257</v>
       </c>
       <c r="B42" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>128466277</v>
       </c>
       <c r="B43" t="n">
-        <v>96744</v>
+        <v>96751</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5430,7 +5430,7 @@
         <v>128466236</v>
       </c>
       <c r="B44" t="n">
-        <v>91519</v>
+        <v>91524</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
